--- a/Data/PreMauryaPeriod.xlsx
+++ b/Data/PreMauryaPeriod.xlsx
@@ -472,828 +472,828 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
+          <t>Who was the first king to annex Kashi into Magadha?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The first Buddhist Council was held during the reign of:</t>
+          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
+          <t>The term 'Purohita' in ancient times referred to:</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>King</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Army commander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
+          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Decline of tribalism</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Agricultural surplus</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Republic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>In the 6th century BCE, Magadha had its early capital at:</t>
+          <t>Which Mahajanapada had a significant role in early Jainism?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Champanagar</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
+          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Atheism</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Materialism</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
+          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Decline of tribalism</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Agricultural surplus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Mahajanapada is often associated with early republicanism?</t>
+          <t>In Pre-Mauryan India, coins were typically made of:</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
+          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Atheism</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Materialism</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had a significant role in early Jainism?</t>
+          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Who among the following was a contemporary of Buddha?</t>
+          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
+          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Ajatashatru</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mahapadma Nanda</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Bimbisara</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Mahapadma Nanda</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Dhanananda</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The term ‘Rajagriha’ refers to:</t>
+          <t>Which Mahajanapada had its capital at Taxila?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A religious text</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A king’s court</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A coin</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
+          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Religious groups</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Malla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trade guilds</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
+          <t>Alexander's invasion took place during the reign of:</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
+          <t>Who was the founder of the Haryanka dynasty?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Farmer</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The term 'Sangha' in ancient Indian context implies:</t>
+          <t>In which language were the early Buddhist texts written?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Political monarchy</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Military council</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Religious sect only</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who was the founder of the Haryanka dynasty?</t>
+          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
+          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Republic</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan India, coins were typically made of:</t>
+          <t>The term ‘Mahajanapada’ refers to:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Minor tribes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Religious sects</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was known for its republican form of government?</t>
+          <t>Who among the following was a contemporary of Buddha?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The major trade route during the Pre-Mauryan period connected:</t>
+          <t>The capital of the Avanti Mahajanapada was:</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rajagriha to Ujjain</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ujjain to Madurai</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mathura to Kanchipuram</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who was the last king of the Shishunaga dynasty?</t>
+          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kakavarna</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nandivardhana</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1336,16 +1336,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Taxila?</t>
+          <t>Which of the following was a republican Mahajanapada?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1355,89 +1355,89 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Lichchhavis were part of which confederacy?</t>
+          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Jataka Tales</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The capital of the Vajji confederacy was:</t>
+          <t>Who is credited with founding the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1480,371 +1480,371 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which of the following was a republican Mahajanapada?</t>
+          <t>The capital of the Vajji confederacy was:</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Nanda dynasty was overthrown by:</t>
+          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Who is credited with founding the city of Pataliputra?</t>
+          <t>The religious reformer Makkhali Gosala was associated with:</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Lokayata</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The main source of revenue for Mahajanapadas was:</t>
+          <t>The Nanda dynasty was overthrown by:</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tribute</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salt tax</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alexander's invasion took place during the reign of:</t>
+          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Chandragupta Maurya</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Dhanananda</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
+          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vinaya Pitaka</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Religious groups</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Digha Nikaya</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Majjhima Nikaya</t>
+          <t>Trade guilds</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
+          <t>What was the political structure of the Lichchhavis?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The main occupation of the people in Janapadas was:</t>
+          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Mobile walls</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>War drum</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
+          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Mathura?</t>
+          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
+          <t>The Nandas were overthrown by which political strategist?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1854,629 +1854,629 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
+          <t>Who is considered the first historical ruler of Magadha?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Vatsa Mahajanapada had its capital at:</t>
+          <t>The first Buddhist Council was held during the reign of:</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The term ‘Mahajanapada’ refers to:</t>
+          <t>Which Mahajanapada was known for its republican form of government?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Minor tribes</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Religious sects</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The capital of the Avanti Mahajanapada was:</t>
+          <t>The term 'Sangha' in ancient Indian context implies:</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Political monarchy</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Military council</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Religious sect only</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which king is said to have constructed the city of Pataliputra?</t>
+          <t>The main occupation of the people in Janapadas was:</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
+          <t>The capital of the Kuru Mahajanapada was:</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chariots</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cannons</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bow and arrow</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Who is considered the first historical ruler of Magadha?</t>
+          <t>Who was the last king of the Shishunaga dynasty?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Kakavarna</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Nandivardhana</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
+          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Farmer</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
+          <t>The main source of revenue for Mahajanapadas was:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Tribute</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Salt tax</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
+          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jataka Tales</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Deimachus</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
+          <t>The Lichchhavis were part of which confederacy?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mobile walls</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>War drum</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The term 'Purohita' in ancient times referred to:</t>
+          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Army commander</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The term “Janapada” literally means:</t>
+          <t>Which Mahajanapada is often associated with early republicanism?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tribal Leader</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chief of a region</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Land revenue</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
+          <t>The term ‘Rajagriha’ refers to:</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>A religious text</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>A king’s court</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>A coin</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Lichchhavis were associated with which famous sage?</t>
+          <t>The main reason behind Magadha’s rise was:</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Military power</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Maitreya</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Religious influence</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brahmanaspati</t>
+          <t>Greek alliances</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who was the first king to annex Kashi into Magadha?</t>
+          <t>Which Mahajanapada was located around modern-day Bihar?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
+          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Vinaya Pitaka</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Digha Nikaya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Majjhima Nikaya</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2488,612 +2488,612 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
+          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Malla</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which text mentions 16 Mahajanapadas?</t>
+          <t>The Vatsa Mahajanapada had its capital at:</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
+          <t>Who was the founder of the Nanda dynasty?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located around modern-day Bihar?</t>
+          <t>In the 6th century BCE, Magadha had its early capital at:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Champanagar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The religious reformer Makkhali Gosala was associated with:</t>
+          <t>Which Mahajanapada had its capital at Mathura?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokayata</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which of these was known as a strong military power before the Mauryas?</t>
+          <t>The Lichchhavis were associated with which famous sage?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Maitreya</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Brahmanaspati</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
+          <t>Which text mentions 16 Mahajanapadas?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Nandas were overthrown by which political strategist?</t>
+          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Kushan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The main reason behind Magadha’s rise was:</t>
+          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Military power</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Religious influence</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Greek alliances</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
+          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Deimachus</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>In which language were the early Buddhist texts written?</t>
+          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
+          <t>The major trade route during the Pre-Mauryan period connected:</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rajagriha to Ujjain</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Ujjain to Madurai</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Mathura to Kanchipuram</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The capital of the Kuru Mahajanapada was:</t>
+          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What was the political structure of the Lichchhavis?</t>
+          <t>Which king is said to have constructed the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Who was the founder of the Nanda dynasty?</t>
+          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Chariots</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Cannons</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Bow and arrow</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
+          <t>Which of these was known as a strong military power before the Mauryas?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
+          <t>The term “Janapada” literally means:</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Tribal Leader</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Chief of a region</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>Land revenue</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3136,36 +3136,36 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
+          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/PreMauryaPeriod.xlsx
+++ b/Data/PreMauryaPeriod.xlsx
@@ -472,67 +472,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who was the first king to annex Kashi into Magadha?</t>
+          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
+          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Vinaya Pitaka</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Digha Nikaya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Majjhima Nikaya</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,496 +544,496 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The term 'Purohita' in ancient times referred to:</t>
+          <t>Which of the following was a republican Mahajanapada?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Army commander</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
+          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Republic</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had a significant role in early Jainism?</t>
+          <t>The main occupation of the people in Janapadas was:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
+          <t>Who was the last ruler of the Nanda dynasty?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atheism</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Materialism</t>
+          <t>Nandivardhana</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
+          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Decline of tribalism</t>
+          <t>Farmer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agricultural surplus</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan India, coins were typically made of:</t>
+          <t>Which Mahajanapada was located around modern-day Bihar?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
+          <t>The capital of the Vajji confederacy was:</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
+          <t>The term “Janapada” literally means:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Tribal Leader</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Chief of a region</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Land revenue</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
+          <t>In which language were the early Buddhist texts written?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
+          <t>Which Mahajanapada had its capital at Mathura?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Taxila?</t>
+          <t>The main reason behind Magadha’s rise was:</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Military power</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Religious influence</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Greek alliances</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
+          <t>What was the political structure of the Lichchhavis?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malla</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alexander's invasion took place during the reign of:</t>
+          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who was the founder of the Haryanka dynasty?</t>
+          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Mahapadma Nanda</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Ajatashatru</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Udayin</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Bindusara</t>
@@ -1041,1427 +1041,1427 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>In which language were the early Buddhist texts written?</t>
+          <t>The first Buddhist Council was held during the reign of:</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
+          <t>The Vatsa Mahajanapada had its capital at:</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
+          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Kuru</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Kashi</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Vatsa</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Anga</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Kosala</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The term ‘Mahajanapada’ refers to:</t>
+          <t>In the 6th century BCE, Magadha had its early capital at:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Minor tribes</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Religious sects</t>
+          <t>Champanagar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who among the following was a contemporary of Buddha?</t>
+          <t>The Lichchhavis were part of which confederacy?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The capital of the Avanti Mahajanapada was:</t>
+          <t>The Lichchhavis were associated with which famous sage?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Maitreya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Brahmanaspati</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
+          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which river valley was most important to the rise of Magadha?</t>
+          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tungabhadra</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of the following was a republican Mahajanapada?</t>
+          <t>The Nanda dynasty was overthrown by:</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
+          <t>The capital of the Kuru Mahajanapada was:</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jataka Tales</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Who is credited with founding the city of Pataliputra?</t>
+          <t>Which river valley was most important to the rise of Magadha?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Tungabhadra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Who was the last ruler of the Nanda dynasty?</t>
+          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Ajatashatru</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bimbisara</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Dhanananda</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Udayin</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Nandivardhana</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The capital of the Vajji confederacy was:</t>
+          <t>Alexander's invasion took place during the reign of:</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
+          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Kushan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Magadha</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Gandhara</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The religious reformer Makkhali Gosala was associated with:</t>
+          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lokayata</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Nanda dynasty was overthrown by:</t>
+          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ajatashatru</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mahapadma Nanda</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Bimbisara</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Ashoka</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Alexander</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Chandragupta Maurya</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
+          <t>Which Mahajanapada had a significant role in early Jainism?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
+          <t>Which Mahajanapada is often associated with early republicanism?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Religious groups</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trade guilds</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What was the political structure of the Lichchhavis?</t>
+          <t>Which Mahajanapada was known for its republican form of government?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
+          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Chariots</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mobile walls</t>
+          <t>Cannons</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>War drum</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Bow and arrow</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
+          <t>The term 'Purohita' in ancient times referred to:</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>King</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>Army commander</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
+          <t>Who is considered the first historical ruler of Magadha?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>Chandragupta Maurya</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mahapadma Nanda</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>Bimbisara</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Dhanananda</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Nandas were overthrown by which political strategist?</t>
+          <t>The major trade route during the Pre-Mauryan period connected:</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Rajagriha to Ujjain</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ujjain to Madurai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Mathura to Kanchipuram</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who is considered the first historical ruler of Magadha?</t>
+          <t>The term 'Sangha' in ancient Indian context implies:</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Political monarchy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Military council</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Religious sect only</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The first Buddhist Council was held during the reign of:</t>
+          <t>Who among the following was a contemporary of Buddha?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bindusara</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Bimbisara</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Ajatashatru</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Bimbisara</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bindusara</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was known for its republican form of government?</t>
+          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Kosala</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Avanti</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Gandhara</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Magadha</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Vajji</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Vatsa</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The term 'Sangha' in ancient Indian context implies:</t>
+          <t>Which Mahajanapada had its capital at Taxila?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Political monarchy</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Military council</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Religious sect only</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The main occupation of the people in Janapadas was:</t>
+          <t>The religious reformer Makkhali Gosala was associated with:</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Lokayata</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The capital of the Kuru Mahajanapada was:</t>
+          <t>Who was the founder of the Nanda dynasty?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Who was the last king of the Shishunaga dynasty?</t>
+          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kakavarna</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Mobile walls</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>War drum</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nandivardhana</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
+          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Jataka Tales</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Farmer</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The main source of revenue for Mahajanapadas was:</t>
+          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tribute</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salt tax</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
+          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deimachus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Lichchhavis were part of which confederacy?</t>
+          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Atheism</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Materialism</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
+          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Malla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Mahajanapada is often associated with early republicanism?</t>
+          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Republic</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The term ‘Rajagriha’ refers to:</t>
+          <t>Who was the founder of the Haryanka dynasty?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A religious text</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A king’s court</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A coin</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The main reason behind Magadha’s rise was:</t>
+          <t>Which of these was known as a strong military power before the Mauryas?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Military power</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Religious influence</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Greek alliances</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located around modern-day Bihar?</t>
+          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>Vajji</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>Magadha</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Gandhara</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Magadha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
+          <t>Which text mentions 16 Mahajanapadas?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vinaya Pitaka</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Digha Nikaya</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Majjhima Nikaya</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2488,612 +2488,612 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
+          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Vatsa Mahajanapada had its capital at:</t>
+          <t>Who was the first king to annex Kashi into Magadha?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Who was the founder of the Nanda dynasty?</t>
+          <t>In Pre-Mauryan India, coins were typically made of:</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>In the 6th century BCE, Magadha had its early capital at:</t>
+          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Champanagar</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Mathura?</t>
+          <t>The term ‘Mahajanapada’ refers to:</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Minor tribes</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Religious sects</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Lichchhavis were associated with which famous sage?</t>
+          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Maitreya</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brahmanaspati</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which text mentions 16 Mahajanapadas?</t>
+          <t>Who was the last king of the Shishunaga dynasty?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Kakavarna</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Nandivardhana</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
+          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Decline of tribalism</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Agricultural surplus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
+          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
+          <t>The term ‘Rajagriha’ refers to:</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>A religious text</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>A king’s court</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>A coin</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
+          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Deimachus</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The major trade route during the Pre-Mauryan period connected:</t>
+          <t>Which king is said to have constructed the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Rajagriha to Ujjain</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ujjain to Madurai</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mathura to Kanchipuram</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
+          <t>Who is credited with founding the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which king is said to have constructed the city of Pataliputra?</t>
+          <t>The capital of the Avanti Mahajanapada was:</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
+          <t>The main source of revenue for Mahajanapadas was:</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chariots</t>
+          <t>Tribute</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cannons</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bow and arrow</t>
+          <t>Salt tax</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which of these was known as a strong military power before the Mauryas?</t>
+          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The term “Janapada” literally means:</t>
+          <t>The Nandas were overthrown by which political strategist?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tribal Leader</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chief of a region</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Land revenue</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3136,36 +3136,36 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
+          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Religious groups</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Trade guilds</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/PreMauryaPeriod.xlsx
+++ b/Data/PreMauryaPeriod.xlsx
@@ -472,201 +472,201 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
+          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
+          <t>Which Mahajanapada had its capital at Mathura?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vinaya Pitaka</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Digha Nikaya</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Majjhima Nikaya</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of the following was a republican Mahajanapada?</t>
+          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
+          <t>Which Mahajanapada is often associated with early republicanism?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Magadha</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kashi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vajji</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Kuru</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Magadha</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Kashi</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Panchala</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The main occupation of the people in Janapadas was:</t>
+          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Kushan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who was the last ruler of the Nanda dynasty?</t>
+          <t>Who was the founder of the Haryanka dynasty?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -676,1051 +676,1051 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nandivardhana</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
+          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Farmer</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Deimachus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located around modern-day Bihar?</t>
+          <t>The Vatsa Mahajanapada had its capital at:</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The capital of the Vajji confederacy was:</t>
+          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Decline of tribalism</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Agricultural surplus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The term “Janapada” literally means:</t>
+          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tribal Leader</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chief of a region</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Land revenue</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>In which language were the early Buddhist texts written?</t>
+          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Atheism</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Materialism</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Mathura?</t>
+          <t>Alexander's invasion took place during the reign of:</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The main reason behind Magadha’s rise was:</t>
+          <t>Who was the founder of the Nanda dynasty?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Military power</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Religious influence</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Greek alliances</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What was the political structure of the Lichchhavis?</t>
+          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
+          <t>Which Mahajanapada was known for its republican form of government?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Avanti</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Gandhara</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Vajji</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Kamboja</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Gandhara</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
+          <t>Who is credited with founding the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Ajatashatru</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Mahapadma Nanda</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The first Buddhist Council was held during the reign of:</t>
+          <t>The Nanda dynasty was overthrown by:</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Bimbisara</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ajatashatru</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Vatsa Mahajanapada had its capital at:</t>
+          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
+          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Jataka Tales</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>In the 6th century BCE, Magadha had its early capital at:</t>
+          <t>In Pre-Mauryan India, coins were typically made of:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Champanagar</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Lichchhavis were part of which confederacy?</t>
+          <t>The term 'Purohita' in ancient times referred to:</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>King</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Army commander</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Lichchhavis were associated with which famous sage?</t>
+          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Maitreya</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brahmanaspati</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
+          <t>The capital of the Avanti Mahajanapada was:</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
+          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Republic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Nanda dynasty was overthrown by:</t>
+          <t>Which Mahajanapada had its capital at Taxila?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The capital of the Kuru Mahajanapada was:</t>
+          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which river valley was most important to the rise of Magadha?</t>
+          <t>Which of these was known as a strong military power before the Mauryas?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tungabhadra</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
+          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bimbisara</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Ajatashatru</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Bimbisara</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Dhanananda</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alexander's invasion took place during the reign of:</t>
+          <t>Which text mentions 16 Mahajanapadas?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
+          <t>The term 'Sangha' in ancient Indian context implies:</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Political monarchy</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Military council</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>Religious sect only</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
+          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Religious groups</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Trade guilds</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
+          <t>The main occupation of the people in Janapadas was:</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had a significant role in early Jainism?</t>
+          <t>The main reason behind Magadha’s rise was:</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Military power</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Religious influence</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Greek alliances</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which Mahajanapada is often associated with early republicanism?</t>
+          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was known for its republican form of government?</t>
+          <t>Which of the following was a republican Mahajanapada?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Kosala</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Magadha</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Vajji</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Avanti</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Gandhara</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Vajji</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Vatsa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1732,1211 +1732,1211 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
+          <t>The first Buddhist Council was held during the reign of:</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chariots</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cannons</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bow and arrow</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The term 'Purohita' in ancient times referred to:</t>
+          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Army commander</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who is considered the first historical ruler of Magadha?</t>
+          <t>Who was the last king of the Shishunaga dynasty?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Kakavarna</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Nandivardhana</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The major trade route during the Pre-Mauryan period connected:</t>
+          <t>Which Mahajanapada had a significant role in early Jainism?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Rajagriha to Ujjain</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ujjain to Madurai</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mathura to Kanchipuram</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The term 'Sangha' in ancient Indian context implies:</t>
+          <t>In which language were the early Buddhist texts written?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Political monarchy</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Military council</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Religious sect only</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who among the following was a contemporary of Buddha?</t>
+          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
+          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Taxila?</t>
+          <t>Which Mahajanapada was ruled by King Pradyota?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The religious reformer Makkhali Gosala was associated with:</t>
+          <t>The capital of the Kuru Mahajanapada was:</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lokayata</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Who was the founder of the Nanda dynasty?</t>
+          <t>What was the political structure of the Lichchhavis?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
+          <t>The term “Janapada” literally means:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Tribal Leader</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mobile walls</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>War drum</t>
+          <t>Chief of a region</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Land revenue</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
+          <t>Who is considered the first historical ruler of Magadha?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jataka Tales</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
+          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
+          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
+          <t>Which Mahajanapada was located around modern-day Bihar?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Atheism</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Materialism</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
+          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Vinaya Pitaka</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Malla</t>
+          <t>Digha Nikaya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Majjhima Nikaya</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
+          <t>Who was the last ruler of the Nanda dynasty?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Republic</t>
+          <t>Nandivardhana</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who was the founder of the Haryanka dynasty?</t>
+          <t>The religious reformer Makkhali Gosala was associated with:</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Lokayata</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which of these was known as a strong military power before the Mauryas?</t>
+          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Chariots</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Cannons</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Bow and arrow</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
+          <t>Who was the first king to annex Kashi into Magadha?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which text mentions 16 Mahajanapadas?</t>
+          <t>In the 6th century BCE, Magadha had its early capital at:</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Champanagar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
+          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was the first king to annex Kashi into Magadha?</t>
+          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Malla</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan India, coins were typically made of:</t>
+          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Farmer</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
+          <t>The capital of the Vajji confederacy was:</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The term ‘Mahajanapada’ refers to:</t>
+          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Minor tribes</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Religious sects</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
+          <t>The term ‘Rajagriha’ refers to:</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>A religious text</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>A king’s court</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>A coin</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who was the last king of the Shishunaga dynasty?</t>
+          <t>The Lichchhavis were associated with which famous sage?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kakavarna</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Maitreya</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nandivardhana</t>
+          <t>Brahmanaspati</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
+          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Decline of tribalism</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Agricultural surplus</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
+          <t>The major trade route during the Pre-Mauryan period connected:</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Rajagriha to Ujjain</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Ujjain to Madurai</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Mathura to Kanchipuram</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The term ‘Rajagriha’ refers to:</t>
+          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A religious text</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>A king’s court</t>
+          <t>Mobile walls</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>War drum</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>A coin</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
+          <t>The term ‘Mahajanapada’ refers to:</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>Minor tribes</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Deimachus</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Religious sects</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which king is said to have constructed the city of Pataliputra?</t>
+          <t>The Nandas were overthrown by which political strategist?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who is credited with founding the city of Pataliputra?</t>
+          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>Ajatashatru</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Ashoka</t>
-        </is>
-      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Bimbisara</t>
@@ -2944,228 +2944,228 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The capital of the Avanti Mahajanapada was:</t>
+          <t>The main source of revenue for Mahajanapadas was:</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Tribute</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Salt tax</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The main source of revenue for Mahajanapadas was:</t>
+          <t>Who among the following was a contemporary of Buddha?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tribute</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Salt tax</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
+          <t>The Lichchhavis were part of which confederacy?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Nandas were overthrown by which political strategist?</t>
+          <t>Which king is said to have constructed the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>Ajatashatru</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Chanakya</t>
-        </is>
-      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was ruled by King Pradyota?</t>
+          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
+          <t>Which river valley was most important to the rise of Magadha?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Religious groups</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trade guilds</t>
+          <t>Tungabhadra</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/PreMauryaPeriod.xlsx
+++ b/Data/PreMauryaPeriod.xlsx
@@ -472,211 +472,211 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
+          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Chariot</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Mobile walls</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>War drum</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Rotating blade chariot</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Mathura?</t>
+          <t>The term ‘Mahajanapada’ refers to:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Minor tribes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Religious sects</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Surasena</t>
+          <t>Great kingdoms</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
+          <t>The Nandas were overthrown by which political strategist?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Mahajanapada is often associated with early republicanism?</t>
+          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
+          <t>The main source of revenue for Mahajanapadas was:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maurya</t>
+          <t>Tribute</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>Salt tax</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Land tax</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who was the founder of the Haryanka dynasty?</t>
+          <t>Who among the following was a contemporary of Buddha?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bindusara</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Bimbisara</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ajatashatru</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Udayin</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -688,2484 +688,2484 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
+          <t>The Lichchhavis were part of which confederacy?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deimachus</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Vatsa Mahajanapada had its capital at:</t>
+          <t>Which king is said to have constructed the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
+          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Urbanization</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Decline of tribalism</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Agricultural surplus</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Upanishads</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
+          <t>Which river valley was most important to the rise of Magadha?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Tungabhadra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
+          <t>In the 6th century BCE, Magadha had its early capital at:</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Atheism</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Materialism</t>
+          <t>Champanagar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Determinism</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alexander's invasion took place during the reign of:</t>
+          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who was the founder of the Nanda dynasty?</t>
+          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Malla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
+          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Shishunaga</t>
+          <t>Soldier</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Farmer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haryanka</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Minister</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was known for its republican form of government?</t>
+          <t>The capital of the Vajji confederacy was:</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Pataliputra</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who is credited with founding the city of Pataliputra?</t>
+          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Nanda dynasty was overthrown by:</t>
+          <t>The term ‘Rajagriha’ refers to:</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>A religious text</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>A king’s court</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>A coin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>A capital city</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
+          <t>The Lichchhavis were associated with which famous sage?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Vashistha</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Maitreya</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Brahmanaspati</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
+          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jataka Tales</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manusmriti</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan India, coins were typically made of:</t>
+          <t>The major trade route during the Pre-Mauryan period connected:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Rajagriha to Ujjain</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Ujjain to Madurai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Mathura to Kanchipuram</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Punch-marked silver</t>
+          <t>Pataliputra to Taxila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The term 'Purohita' in ancient times referred to:</t>
+          <t>The term “Janapada” literally means:</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Tribal Leader</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Chief of a region</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Army commander</t>
+          <t>Land revenue</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Territory of a tribe</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
+          <t>Who is considered the first historical ruler of Magadha?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Chandragupta Maurya</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Mahapadma Nanda</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Bimbisara</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The capital of the Avanti Mahajanapada was:</t>
+          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kausambi</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
+          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Republic</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had its capital at Taxila?</t>
+          <t>Which Mahajanapada was located around modern-day Bihar?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Avanti</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vatsa</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Magadha</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Gandhara</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Magadha</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Vatsa</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Kamboja</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Gandhara</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
+          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Vinaya Pitaka</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Digha Nikaya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Majjhima Nikaya</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which of these was known as a strong military power before the Mauryas?</t>
+          <t>Who was the last ruler of the Nanda dynasty?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Nandivardhana</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nanda Empire</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
+          <t>The religious reformer Makkhali Gosala was associated with:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Lokayata</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Ajivikas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which text mentions 16 Mahajanapadas?</t>
+          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vedas</t>
+          <t>Chariots</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Cannons</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Bow and arrow</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Catapults (Mahashilakantaka)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The term 'Sangha' in ancient Indian context implies:</t>
+          <t>Who was the first king to annex Kashi into Magadha?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Political monarchy</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Military council</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Religious sect only</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Republican assembly</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
+          <t>The first Buddhist Council was held during the reign of:</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Religious groups</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trade guilds</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Democratic republics</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The main occupation of the people in Janapadas was:</t>
+          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The main reason behind Magadha’s rise was:</t>
+          <t>Who was the last king of the Shishunaga dynasty?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Military power</t>
+          <t>Kakavarna</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Religious influence</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greek alliances</t>
+          <t>Nandivardhana</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Strategic location</t>
+          <t>Kalashoka</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
+          <t>Which Mahajanapada had a significant role in early Jainism?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which of the following was a republican Mahajanapada?</t>
+          <t>In which language were the early Buddhist texts written?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The first Buddhist Council was held during the reign of:</t>
+          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Magadhan king introduced the practice of matrimonial alliances?</t>
+          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mahapadma Nanda</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Ajatashatru</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bimbisara</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bindusara</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Mahapadma Nanda</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Dhanananda</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who was the last king of the Shishunaga dynasty?</t>
+          <t>Which Mahajanapada was ruled by King Pradyota?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kakavarna</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nandivardhana</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Kalashoka</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Mahajanapada had a significant role in early Jainism?</t>
+          <t>The capital of the Kuru Mahajanapada was:</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Indraprastha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>In which language were the early Buddhist texts written?</t>
+          <t>What was the political structure of the Lichchhavis?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Confederacy</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay on the easternmost frontier of ancient India?</t>
+          <t>In Pre-Mauryan economy, the punch-marked coins were mostly made of:</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The ‘Sanskritisation’ of Magadha happened under which ruler?</t>
+          <t>Which of these was known as a strong military power before the Mauryas?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Nanda Empire</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was ruled by King Pradyota?</t>
+          <t>Who is considered as the "Destroyer of Kshatriyas" according to the Puranas?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vatsa</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The capital of the Kuru Mahajanapada was:</t>
+          <t>Which text mentions 16 Mahajanapadas?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>Vedas</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Indraprastha</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What was the political structure of the Lichchhavis?</t>
+          <t>The term 'Sangha' in ancient Indian context implies:</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Political monarchy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oligarchy</t>
+          <t>Military council</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Religious sect only</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Confederacy</t>
+          <t>Republican assembly</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The term “Janapada” literally means:</t>
+          <t>The term 'Gana' or 'Sangha' in ancient polity referred to:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tribal Leader</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Religious groups</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chief of a region</t>
+          <t>Village councils</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Land revenue</t>
+          <t>Trade guilds</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Territory of a tribe</t>
+          <t>Democratic republics</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who is considered the first historical ruler of Magadha?</t>
+          <t>The main occupation of the people in Janapadas was:</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>How many Mahajanapadas were mentioned in the Anguttara Nikaya?</t>
+          <t>The main reason behind Magadha’s rise was:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Military power</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Religious influence</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Greek alliances</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Strategic location</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which of the following Mahajanapadas was located in modern-day Punjab?</t>
+          <t>The ancient city of Champa was the capital of which Mahajanapada?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Kosala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gandhara</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which Mahajanapada was located around modern-day Bihar?</t>
+          <t>Which of the following was a republican Mahajanapada?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Kosala</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Magadha</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Vajji</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>Avanti</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Vatsa</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Magadha</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Gandhara</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The word 'Mahajanapada' is found in which Buddhist text?</t>
+          <t>Who is credited with founding the city of Pataliputra?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vinaya Pitaka</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Digha Nikaya</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Majjhima Nikaya</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Who was the last ruler of the Nanda dynasty?</t>
+          <t>The Nanda dynasty was overthrown by:</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nandivardhana</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The religious reformer Makkhali Gosala was associated with:</t>
+          <t>Which ancient river is closely associated with the Gandhara Mahajanapada?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lokayata</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ajivikas</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ajatashatru used which war instrument against the Lichchhavis?</t>
+          <t>The earliest mention of 16 Mahajanapadas is found in:</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chariots</t>
+          <t>Jataka Tales</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cannons</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bow and arrow</t>
+          <t>Manusmriti</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Catapults (Mahashilakantaka)</t>
+          <t>Anguttara Nikaya</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who was the first king to annex Kashi into Magadha?</t>
+          <t>In Pre-Mauryan India, coins were typically made of:</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Udayin</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mahapadma Nanda</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Punch-marked silver</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>In the 6th century BCE, Magadha had its early capital at:</t>
+          <t>The term 'Purohita' in ancient times referred to:</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>King</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Champanagar</t>
+          <t>Army commander</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Priest</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The kingdom of Kashi was eventually absorbed by which Mahajanapada?</t>
+          <t>Which Pre-Mauryan king built fortifications around Rajagriha?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Mahajanapada lay to the northwest of the Indian subcontinent?</t>
+          <t>The capital of the Avanti Mahajanapada was:</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malla</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>In early Magadhan administration, the post of Amatya was equivalent to:</t>
+          <t>What was the dominant mode of polity in Magadha during the Nanda period?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Soldier</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Farmer</t>
+          <t>Oligarchy</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Republic</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Minister</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The capital of the Vajji confederacy was:</t>
+          <t>Which Mahajanapada had its capital at Taxila?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pataliputra</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which was the most powerful Mahajanapada during the rise of Buddhism?</t>
+          <t>Who was the founder of the Haryanka dynasty?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kuru</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Udayin</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Panchala</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The term ‘Rajagriha’ refers to:</t>
+          <t>Who was the ambassador sent by Seleucus I to the Maurya court?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A religious text</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A king’s court</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>Deimachus</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>A coin</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A capital city</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Lichchhavis were associated with which famous sage?</t>
+          <t>The Vatsa Mahajanapada had its capital at:</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vashistha</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Maitreya</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brahmanaspati</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Kausambi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Who among the following used a war engine called ‘Mahashilakantaka’?</t>
+          <t>The Janapadas were transformed into Mahajanapadas due to:</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Urbanization</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Decline of tribalism</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Agricultural surplus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The major trade route during the Pre-Mauryan period connected:</t>
+          <t>Which Mahajanapada was located between the Ganga and Yamuna rivers?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Rajagriha to Ujjain</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ujjain to Madurai</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mathura to Kanchipuram</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pataliputra to Taxila</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The term ‘Rathamusala’ refers to what in ancient warfare?</t>
+          <t>Ajivikas, a sect during Pre-Mauryan period, believed in:</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chariot</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mobile walls</t>
+          <t>Atheism</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>War drum</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Materialism</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rotating blade chariot</t>
+          <t>Determinism</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The term ‘Mahajanapada’ refers to:</t>
+          <t>Alexander's invasion took place during the reign of:</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Village councils</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Minor tribes</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Religious sects</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Great kingdoms</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Nandas were overthrown by which political strategist?</t>
+          <t>Who was the founder of the Nanda dynasty?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Dhanananda</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Mahapadma Nanda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which Pre-Mauryan ruler is known to have convened the First Buddhist Council?</t>
+          <t>Which dynasty immediately preceded the Mauryas in Magadha?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dhanananda</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The main source of revenue for Mahajanapadas was:</t>
+          <t>Which Mahajanapada was known for its republican form of government?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tribute</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Salt tax</t>
+          <t>Vatsa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Land tax</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Who among the following was a contemporary of Buddha?</t>
+          <t>Which dynasty introduced the concept of hereditary monarchy in Magadha?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Shishunaga</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Haryanka</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Lichchhavis were part of which confederacy?</t>
+          <t>Which Mahajanapada had its capital at Mathura?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kosala</t>
+          <t>Panchala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Gandhara</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Vajji</t>
+          <t>Surasena</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which king is said to have constructed the city of Pataliputra?</t>
+          <t>The Shishunaga dynasty was succeeded by which dynasty?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which ancient Indian text contains references to Mahajanapadas?</t>
+          <t>Which Mahajanapada is often associated with early republicanism?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Upanishads</t>
+          <t>Kuru</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anguttara Nikaya</t>
+          <t>Vajji</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which river valley was most important to the rise of Magadha?</t>
+          <t>Which of the following kingdoms was prominent during the 6th century BCE?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Maurya</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tungabhadra</t>
+          <t>Kushan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
